--- a/grading_results_rag_metrics.xlsx
+++ b/grading_results_rag_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UEH\Downloads\17. Đề án tốt nghiệp\rag\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\rag\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C559FD-C94B-4AD7-9237-84F85CB16F5D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E992B9EF-D0BB-483C-B1F7-9FE77F3B61B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="690" windowWidth="24060" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="91">
   <si>
     <t>Chiến lược kinh doanh thương mại điện tử</t>
   </si>
@@ -28,48 +28,12 @@
     <t>nhom1.pdf</t>
   </si>
   <si>
-    <t>ĐẠI HỌC KINH TẾ TP. HỒ CHÍ MINH
-TRƯỜNG CÔNG NGHỆ VÀ THIẾT KẾ UEH
-KHOA CÔNG NGHỆ THÔNG TIN KINH DOANH
-Báo cáo cuối kỳ
-XÂY DỰNG CHIẾN LƯỢC GIÁ CHO SẢN PHẨM
-ROBOT HÚT BỤI ZBOT
-Bộ môn : Chiến lược kinh doanh Thương mại điện tử
-Giảng viên hướng dẫn : TS. Nguyễn Thành Huy
-Mã lớp học phần : 23C1INF50902903...</t>
-  </si>
-  <si>
-    <t>6.8</t>
-  </si>
-  <si>
     <t>nhom5.pdf</t>
   </si>
   <si>
-    <t>BỘ GIÁO DỤC VÀ ĐÀO TẠO
-TRƯỜNG KINH DOANH
-KHOA CÔNG NGHỆ THÔNG TIN KINH DOANH
-BÁO CÁO CUỐI KỲ MÔN HỌC:
-CHIẾN LƯỢC KINH DOANH THƯƠNG MẠI ĐIỆN TỬ
-Tên đề tài: XÂY DỰNG CHIẾN LƯỢC KINH DOANH THƯƠNG MẠI
-ĐIỆN TỬ CHO CÔNG TY SẢN PHẨM THÚ CƯNG PETTIES THÔNG
-QUA MARKETING VÀ PROMOTION
-Giảng viên hướng dẫn : T...</t>
-  </si>
-  <si>
     <t>nhom6.pdf</t>
   </si>
   <si>
-    <t>ĐẠI HỌC KINH TẾ TP. HỒ CHÍ MINH
-KHOA CÔNG NGHỆ THÔNG TIN KINH DOANH
-BÁO CÁO ĐỒ ÁN KẾT THÚC HỌC PHẦN
-CHIẾN LƯỢC KINH DOANH THƯƠNG MẠI ĐIỆN TỬ
-Đề tài: Xây dựng chiến lược kinh doanh thương mại điện tử cho
-sản phẩm Yến sào - NCK
-Giảng viên hướng dẫn: TS. Nguyễn Thành Huy
-Mã LHP: 23C1INF50902903
-Nhóm th...</t>
-  </si>
-  <si>
     <t>7.8</t>
   </si>
   <si>
@@ -79,283 +43,19 @@
     <t>nhom2.pdf</t>
   </si>
   <si>
-    <t>ĐẠI HỌC UEH
-TRƯỜNG CÔNG NGHỆ VÀ THIẾT KẾ
-KHOA CÔNG NGHỆ THÔNG TIN KINH DOANH
-BỘ MÔN HỆ THỐNG THANH TOÁN ĐIỆN TỬ
-BÁO CÁO ĐỒ ÁN HỌC PHẦN HỆ THỐNG THANH TOÁN ĐIỆN TỬ
-Đề Tài: Phân tích hệ thống thanh toán NAPAS
-Giảng viên hướng dẫn : Nguyễn Thành Huy
-Mã học phần : 24D1INF50903001
-Thực hiện bởi : Nhóm 2
-...</t>
-  </si>
-  <si>
-    <t>ĐẠI HỌC KINH TẾ TP. HỒ CHÍ MINH
-TRƯỜNG CÔNG NGHỆ VÀ THIẾT KẾ
-KHOA CÔNG NGHỆ THÔNG TIN KINH DOANH
-BỘ MÔN HỆ THỐNG THANH TOÁN ĐIỆN TỬ
-BÁO CÁO DỰ ÁN
-HỆ THỐNG THANH TOÁN ĐIỆN TỬ
-Đề tài: TÌM HIỂU HỆ THỐNG SMART BANKING TRONG THANH TOÁN
-ĐIỆN TỬ TẠI VIỆT NAM
-GVHD: TS. NGUYỄN THÀNH HUY
-Nhóm thực hiện: Nhóm ...</t>
-  </si>
-  <si>
     <t>Marketing kỹ thuật số</t>
   </si>
   <si>
-    <t>ĐẠI HỌC KINH TẾ TP. HỒ CHÍ MINH
-TRƯỜNG CÔNG NGHỆ VÀ THIẾT KẾ
-| KHOA CÔNG NGHỆ THÔNG TIN KINH DOANH
-ĐỒ ÁN CUỐI KỲ
-Chiến Lược Marketing Kỹ Thuật Số Cho
-Sản Phẩm Xốt Ướp Thịt Kiểu Hàn Quốc Cholimex Food
-Học phần: MARKETING KỸ THUẬT SỐ
-Mã lớp học phần: 24C1INF50903201
-Giảng viên hướng dẫn: TS. Nguyễn Th...</t>
-  </si>
-  <si>
     <t>nhom4.pdf</t>
   </si>
   <si>
-    <t>ĐẠI HỌC KINH TẾ TP. HỒ CHÍ MINH
-TRƯỜNG CÔNG NGHỆ VÀ THIẾT KẾ
-| KHOA CÔNG NGHỆ THÔNG TIN KINH DOANH
-BÁO CÁO CUỐI KỲ
-Chiến lượ c Digital Marketing
-Sản phẩm: Máy tính khoa học FLEXIO FX799VN
-Môn học: DIGITAL MARKETING
-Mã lớp họ c phần: 24D1INF50906401
-Giảng viên hướng dẫn: ThS. Nguyễn Thành Huy
-Nhóm si...</t>
-  </si>
-  <si>
-    <t>7.2</t>
-  </si>
-  <si>
-    <t>Phát triển ứng dụng thương mại điện tử</t>
-  </si>
-  <si>
-    <t>01_nhom1.pdf</t>
-  </si>
-  <si>
-    <t>ĐẠI HỌC UEH
-ĐẠI HỌC KINH TẾ THÀNH PHỐ HỒ CHÍ MINH
-KHOA CÔNG NGHỆ THÔNG TIN KINH DOANH
-BÁO CÁO DỰ ÁN NGHIÊN CỨU
-Đề tài
-XÂY DỰNG WEBSITE TMĐT CHO CỬA HÀNG KINH
-DOANH VÒNG Ý - USBIBRACELET
-BỘ MÔN: PHÁT TRIỂN ỨNG DỤNG TMĐT
-Giảng viên: Nguyễn Thành Huy
-Mã lớp học phần: 24C1INF50902701
-Nhóm sinh viên thực...</t>
-  </si>
-  <si>
-    <t>01_nhom5.pdf</t>
-  </si>
-  <si>
-    <t>BỘ GIÁO DỤC VÀ ĐÀO TẠO
-ĐH KINH TẾ TP. HCM
-Môn học: Phát triển ứng dụng thương mại điện tử
-Đề tài: WEBSITE CỬA HÀNG LUNA SHOES
-Danh sách nhóm
-1. Lương Thị Mỹ Duyên - 31221024523
-2. Nguyễn Đỗ Quang Hưng - 31221026231
-3. Nguyễn Ngọc Xuân Nam - 31221023784
-4. Võ Thị Mỹ Ngọc - 31221022417
-Giới thiệu chun...</t>
-  </si>
-  <si>
-    <t>01_nhom6.pdf</t>
-  </si>
-  <si>
-    <t>TRƯỜNG ĐẠI HỌC KINH TẾ THÀNH PHỐ HỒ CHÍ MINH
-KHOA CÔNG NGHỆ THÔNG TIN KINH DOANH
------🙞🙜🕮🙞🙜-----
-BÁO CÁO TIỂU LUẬN
-ĐỀ TÀI: XÂY DỰNG WEBSITE BÁN
-NƯỚC HOA
-Giáo viên hướng dẫn: TS. Nguyễn Thành Huy
-Nhóm thực hiện:
-33211025491 – Đỗ Thị Thanh Hải
-33221025092 - Hoàng Anh Việt
-PHÂN CÔNG CÔNG VIỆC
-HỌ TÊN CÔ...</t>
-  </si>
-  <si>
-    <t>01_nhom7.pdf</t>
-  </si>
-  <si>
-    <t>ĐỀ TÀI: WEBSITE CỬA HÀNG GẤU BÔNG JELLYCAT
-A. Nhóm thực hiện:
-1. Trần Kim Ngân - 31221026596
-2. Trần Nhựt Hà Anh - 31221023707
-3. Võ Phan Thái Ngân - 31221025581
-4. Lê Thị Thanh Trang - 31221024831
-5. Nguyễn Huỳnh Diệu Huyền - 31221024830
-B. Cáclayout củahệthống
-1.Trangchủ 2.Trang sảnphẩm
-3.Chi tiết...</t>
-  </si>
-  <si>
     <t>Quản trị dự án thương mại điện tử</t>
   </si>
   <si>
     <t>nhom3.pdf</t>
   </si>
   <si>
-    <t>ĐẠI HỌC KINH TẾ TP. HỒ CHÍ MINH (UEH)
-BÁO CÁO ĐỒ ÁN HỌC PHẦN
-QUẢN LÝ DỰ ÁN THƯƠNG MẠI ĐIỆN TỬ
-Đề tài: DỰ ÁN XÂY DỰNG WEBSITE DU LỊCH
-TÍCH HỢP ADIVAHA
-GVHD: TS. NGUYỄN THÀNH HUY
-Nhóm thực hiện: Nhom_03
-Tiêu Đình Trung 88224020326
-Trần Đỗ Huy Hoàng 88224020328
-Bùi Thị Uyên Uyên 89233020217
-Trịnh Thanh...</t>
-  </si>
-  <si>
     <t>Thương mại điện tử</t>
-  </si>
-  <si>
-    <t>02_nhom9.pdf</t>
-  </si>
-  <si>
-    <t>BỘ GIÁO DỤC VÀ ĐÀO TẠO
-ĐẠI HỌC KINH TẾ TP. HỒ CHÍ MINH
-TIỂU LUẬN THUYẾT TRÌNH
-THƯƠNG MẠI ĐIỆN TỬ
-PHÂN TÍCH MÔ HÌNH KINH DOANH CỦA
-SÀN THƯƠNG MẠI ĐIỆN TỬ SHOPEEFOOD
-TÊN GIẢNG VIÊN : TS. Nguyễn Thành Huy
-MÃ HỌC PHẦN : 25D1INF50901302
-NHÓM : I
-TP. Hồ Chí Minh - 2025
-2
-DANH SÁCH THÀNH VIÊN
-STT Tên thành...</t>
-  </si>
-  <si>
-    <t>02_nhom10.pdf</t>
-  </si>
-  <si>
-    <t>BỘ GIÁO DỤC &amp; ĐÀO TẠO
-ĐẠI HỌC KINH TẾ TPHCM
-KHOA QUẢN TRỊ
-TIỂU LUẬN KẾT THÚC HỌC PHẦN
-MÔN HỌC: THƯƠNG MẠI ĐIỆN TỬ
-Mã lớp HP: 25D1INF50901302 – Nhóm J
-Sinh viên thực hiện: Đinh Văn Đức – 31221022794 (Leader)
-Nguyễn Thị Mỹ Duyên – 31221022909
-Nguyễn Thị Mỹ Hà – 31221026971
-Nguyễn Đức Sơn – 31221024983...</t>
-  </si>
-  <si>
-    <t>03_nhom1.pdf</t>
-  </si>
-  <si>
-    <t>ĐẠI HỌC UEH
-TRƯỜNG KINH DOANH
-TIỂU LUẬN KẾT THÚC HỌC PHẦN
-Môn học: Thương mại điện tử
-Giảng viên dạy: GV Nguyễn Thành Huy
-Mã LHP: 24D1INF50901303
-TP.HCM, ngày 11 tháng 05 năm 2024
-1
-SINH VIÊN THAM GIA LÀM TIỂU LUẬN
-Họ và tên MSSV Phần trăm tham gia
-Lưu Trương Minh Đạt 31211022752 100%
-Vũ Hồ Yến Vy 3...</t>
-  </si>
-  <si>
-    <t>03_nhom3.pdf</t>
-  </si>
-  <si>
-    <t>ĐẠI HỌC UEH
-TRƯỜNG CÔNG NGHỆ VÀ THIẾT KẾ
-KHOA CÔNG NGHỆ THÔNG TIN KINH DOANH
---------***--------
-BÁO CÁO CUỐI KỲ
-MÔN HỌC: THƯƠNG MẠI ĐIỆN TỬ
-ĐỀ TÀI: TRIỂN KHAI DỰ ÁN HỘP HÁO HỨC TRÊN ODOO
-Giảng viên giảng dạy : TS. Nguyễn Thành Huy
-Mã lớp HP : 24D1INF50901303
-Lớp HP : HPTC.I.EM.1
-Nhóm thực hiện : NH...</t>
-  </si>
-  <si>
-    <t>03_nhom6.pdf</t>
-  </si>
-  <si>
-    <t>BỘ GIÁO DỤC VÀ ĐÀO TẠO
-ĐẠI HỌC KINH TẾ TP. HCM
----o0o---
-KHOA QUẢN TRỊ
-THƯƠNG MẠI ĐIỆN TỬ
-ĐỀ TÀI: NỀN TẢNG ĐẶT NƠI LƯU TRÚ TẠI CÁC
-ĐỊA ĐIỂM DU LỊCH Ở VIỆT NAM
-NHÓM: F
-Thành phố Hồ Chí Minh, 2024
-Thông tin các thành viên
-STT Họ và Tên Khóa MSSV
-1 Phạm Nguyễn Mỹ Thi K47 31211024018
-2 Nguyễn Hồ Phương ...</t>
-  </si>
-  <si>
-    <t>04_nhom4.pdf</t>
-  </si>
-  <si>
-    <t>TRƯỜNG ĐẠI HỌC KINH TẾ TP. HỒ CHÍ MINH
-NGÀNH QUẢN TRỊ
-----------
-THƯƠNG MẠI ĐIỆN TỬ
-DỰ ÁN
-SHADERSHACK - CARD ĐỒ HỌA NVIDIA
-NHÓM: E
-GIẢNG VIÊN: Nguyễn Thành Huy
-LHP: 24D1INF50901304
-MỤC LỤC
-DANH SÁCH THÀNH VIÊN NHÓM E ......................................................................
-SHADERS...</t>
-  </si>
-  <si>
-    <t>04_nhom5.pdf</t>
-  </si>
-  <si>
-    <t>ĐẠI HỌC UEH
-TRƯỜNG KINH DOANH
-KHOA QUẢN TRỊ
-NHÓM F
-BÁO CÁO CUỐI KỲ
-Giảng viên: TS. Nguyễn Thành Huy
-Mã học phần: 24D1INF50901304
-Môn học: Thương mại điện tử
-TP Hồ Chí Minh, ngày 8 tháng 5 năm 2024
-1
-NHÓM F – DANH SÁCH THÀNH VIÊN
-STT MSSV Họ và tên
-1 31211025333 Trần Ngọc Kim Ngân
-2 31211025163 Nguyễ...</t>
-  </si>
-  <si>
-    <t>04_nhom6.pdf</t>
-  </si>
-  <si>
-    <t>ĐẠI HỌC UEH
-TIỂU LUẬN
-Môn học: Thương mại điện tử
-KẾ HOẠCH KINH DOANH THƯƠNG MẠI ĐIỆN TỬ GRABMART
-Giảng viên: Nguyễn Thành Huy
-Mã lớp học phần: 24D1INF50901304
-Sinh viên: Trà Hồng Đoan Nhi - 31211020138 - nhóm trưởng
-Nguyễn Thị Hồng Nhung - 31211027984
-Nguyễn Thị Quỳnh Như - 31211023465
-Nguyễn Nhựt ...</t>
   </si>
   <si>
     <t>ĐẠI HỌC UEH
@@ -949,10 +649,10 @@
     <t>content_essays</t>
   </si>
   <si>
-    <t>diem_mo_hinh</t>
-  </si>
-  <si>
     <t>diem_thuc_te</t>
+  </si>
+  <si>
+    <t>diem_mo_hinh_rag</t>
   </si>
 </sst>
 </file>
@@ -991,7 +691,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1295,30 +995,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="51.5703125" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="B1" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="C1" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E1" t="s">
-        <v>125</v>
+        <v>90</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1326,16 +1027,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="E2" s="1">
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1343,16 +1044,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>6.5</v>
+      <c r="E3" s="1">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1360,916 +1061,576 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="E4" s="1">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>6.5</v>
+        <v>4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
+        <v>19</v>
+      </c>
+      <c r="E6" s="1">
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>8</v>
+        <v>22</v>
+      </c>
+      <c r="E7" s="1">
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8">
+        <v>25</v>
+      </c>
+      <c r="E8" s="1">
         <v>7.5</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9">
-        <v>8</v>
+        <v>27</v>
+      </c>
+      <c r="E9" s="1">
+        <v>7.5</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10">
-        <v>5</v>
+        <v>29</v>
+      </c>
+      <c r="E10" s="1">
+        <v>7.5</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11">
+        <v>30</v>
+      </c>
+      <c r="D11" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="E11" s="1">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12">
-        <v>6</v>
+        <v>31</v>
+      </c>
+      <c r="D12" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="E12" s="1">
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="1">
         <v>8</v>
-      </c>
-      <c r="E13">
-        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14">
-        <v>7.4</v>
+        <v>35</v>
+      </c>
+      <c r="E14" s="1">
+        <v>9.5</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="E15" s="1">
         <v>8</v>
-      </c>
-      <c r="E15">
-        <v>7.4</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16">
-        <v>5.9</v>
+        <v>38</v>
+      </c>
+      <c r="E16" s="1">
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="E17" s="1">
         <v>8</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
         <v>40</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18">
-        <v>6.5</v>
+        <v>41</v>
+      </c>
+      <c r="E18" s="1">
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="C19" t="s">
         <v>42</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19">
-        <v>7</v>
+        <v>43</v>
+      </c>
+      <c r="E19" s="1">
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="C20" t="s">
         <v>44</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20">
-        <v>7</v>
+        <v>45</v>
+      </c>
+      <c r="E20" s="1">
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21">
-        <v>6.5</v>
+        <v>47</v>
+      </c>
+      <c r="E21" s="1">
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22">
-        <v>7.5</v>
+        <v>50</v>
+      </c>
+      <c r="E22" s="1">
+        <v>8.9</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23">
-        <v>7.5</v>
+        <v>52</v>
+      </c>
+      <c r="D23" s="1">
+        <v>9.35</v>
+      </c>
+      <c r="E23" s="1">
+        <v>8.6</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24">
-        <v>9</v>
+        <v>55</v>
+      </c>
+      <c r="E24" s="1">
+        <v>7.8</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25">
-        <v>7.5</v>
+        <v>58</v>
+      </c>
+      <c r="E25" s="1">
+        <v>7.8</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E26">
+        <v>60</v>
+      </c>
+      <c r="D26" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="E26" s="1">
         <v>7.5</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27">
-        <v>7</v>
+        <v>63</v>
+      </c>
+      <c r="E27" s="1">
+        <v>9.5</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E28">
-        <v>7.5</v>
+        <v>66</v>
+      </c>
+      <c r="E28" s="1">
+        <v>8.6</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E29">
-        <v>7.5</v>
+        <v>66</v>
+      </c>
+      <c r="E29" s="1">
+        <v>9.5</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C30" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E30">
-        <v>7.5</v>
+        <v>71</v>
+      </c>
+      <c r="E30" s="1">
+        <v>8.5</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="E31">
+        <v>73</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="1">
         <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
-      </c>
-      <c r="D32" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="E32">
-        <v>8</v>
+        <v>75</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="1">
+        <v>7.5</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E33">
+        <v>4</v>
+      </c>
+      <c r="E33" s="1">
         <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="C34" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E34">
-        <v>9.5</v>
+        <v>4</v>
+      </c>
+      <c r="E34" s="1">
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D35" s="1">
-        <v>7.6</v>
-      </c>
-      <c r="E35">
-        <v>8</v>
+        <v>7.3</v>
+      </c>
+      <c r="E35" s="1">
+        <v>7.5</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C36" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E36">
-        <v>9</v>
+      <c r="E36" s="1">
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" s="1">
-        <v>8.4</v>
-      </c>
-      <c r="E37">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>13</v>
-      </c>
-      <c r="B38" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" t="s">
-        <v>75</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E38">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" t="s">
-        <v>77</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E39">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" t="s">
-        <v>79</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E40">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E41">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>30</v>
-      </c>
-      <c r="B42" t="s">
-        <v>83</v>
-      </c>
-      <c r="C42" t="s">
-        <v>84</v>
-      </c>
-      <c r="D42" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E42">
-        <v>8.9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>30</v>
-      </c>
-      <c r="B43" t="s">
-        <v>86</v>
-      </c>
-      <c r="C43" t="s">
-        <v>87</v>
-      </c>
-      <c r="D43" s="1">
-        <v>9.35</v>
-      </c>
-      <c r="E43">
-        <v>8.6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>30</v>
-      </c>
-      <c r="B44" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" t="s">
-        <v>90</v>
-      </c>
-      <c r="E44">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>30</v>
-      </c>
-      <c r="B45" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" t="s">
-        <v>92</v>
-      </c>
-      <c r="D45" t="s">
-        <v>93</v>
-      </c>
-      <c r="E45">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>30</v>
-      </c>
-      <c r="B46" t="s">
-        <v>94</v>
-      </c>
-      <c r="C46" t="s">
-        <v>95</v>
-      </c>
-      <c r="D46" s="1">
-        <v>6.8</v>
-      </c>
-      <c r="E46">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>30</v>
-      </c>
-      <c r="B47" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" t="s">
-        <v>97</v>
-      </c>
-      <c r="D47" t="s">
-        <v>98</v>
-      </c>
-      <c r="E47">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>30</v>
-      </c>
-      <c r="B48" t="s">
-        <v>99</v>
-      </c>
-      <c r="C48" t="s">
-        <v>100</v>
-      </c>
-      <c r="D48" t="s">
-        <v>101</v>
-      </c>
-      <c r="E48">
-        <v>8.6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>30</v>
-      </c>
-      <c r="B49" t="s">
-        <v>102</v>
-      </c>
-      <c r="C49" t="s">
-        <v>103</v>
-      </c>
-      <c r="D49" t="s">
-        <v>101</v>
-      </c>
-      <c r="E49">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>30</v>
-      </c>
-      <c r="B50" t="s">
-        <v>104</v>
-      </c>
-      <c r="C50" t="s">
-        <v>105</v>
-      </c>
-      <c r="D50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E50">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>30</v>
-      </c>
-      <c r="B51" t="s">
-        <v>107</v>
-      </c>
-      <c r="C51" t="s">
-        <v>108</v>
-      </c>
-      <c r="D51" t="s">
-        <v>106</v>
-      </c>
-      <c r="E51">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>30</v>
-      </c>
-      <c r="B52" t="s">
-        <v>109</v>
-      </c>
-      <c r="C52" t="s">
-        <v>110</v>
-      </c>
-      <c r="D52" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>30</v>
-      </c>
-      <c r="B53" t="s">
-        <v>111</v>
-      </c>
-      <c r="C53" t="s">
-        <v>112</v>
-      </c>
-      <c r="D53" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>30</v>
-      </c>
-      <c r="B54" t="s">
-        <v>113</v>
-      </c>
-      <c r="C54" t="s">
-        <v>114</v>
-      </c>
-      <c r="D54" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>30</v>
-      </c>
-      <c r="B55" t="s">
-        <v>115</v>
-      </c>
-      <c r="C55" t="s">
-        <v>116</v>
-      </c>
-      <c r="D55" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="E55">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>30</v>
-      </c>
-      <c r="B56" t="s">
-        <v>117</v>
-      </c>
-      <c r="C56" t="s">
-        <v>118</v>
-      </c>
-      <c r="D56" t="s">
-        <v>8</v>
-      </c>
-      <c r="E56">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>30</v>
-      </c>
-      <c r="B57" t="s">
-        <v>119</v>
-      </c>
-      <c r="C57" t="s">
-        <v>120</v>
-      </c>
-      <c r="D57" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57">
+      <c r="D37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E37" s="1">
         <v>7.5</v>
       </c>
     </row>

--- a/grading_results_rag_metrics.xlsx
+++ b/grading_results_rag_metrics.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\rag\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UEH\Downloads\17. Đề án tốt nghiệp\rag\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E992B9EF-D0BB-483C-B1F7-9FE77F3B61B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE7F4F7-4705-47A4-9288-987B0F69600F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="101">
   <si>
     <t>Chiến lược kinh doanh thương mại điện tử</t>
   </si>
@@ -653,6 +653,36 @@
   </si>
   <si>
     <t>diem_mo_hinh_rag</t>
+  </si>
+  <si>
+    <t>GIỎI</t>
+  </si>
+  <si>
+    <t>&gt;8</t>
+  </si>
+  <si>
+    <t>KHÁ</t>
+  </si>
+  <si>
+    <t>6.5-7.9</t>
+  </si>
+  <si>
+    <t>TRUNG BÌNH</t>
+  </si>
+  <si>
+    <t>5-6.4</t>
+  </si>
+  <si>
+    <t>YẾU</t>
+  </si>
+  <si>
+    <t>&lt;5</t>
+  </si>
+  <si>
+    <t>khá</t>
+  </si>
+  <si>
+    <t>giỏi</t>
   </si>
 </sst>
 </file>
@@ -995,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.42578125" bestFit="1" customWidth="1"/>
@@ -1003,9 +1033,10 @@
     <col min="3" max="3" width="51.5703125" customWidth="1"/>
     <col min="4" max="4" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>86</v>
       </c>
@@ -1021,8 +1052,21 @@
       <c r="E1" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K1" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="L1" t="str">
+        <f>IF(K1&gt;8,"GIỎI", IF(K1&gt;=6.5,"KHÁ", IF(K1&gt;=5,"TRUNG BÌNH","YẾU")))</f>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1038,8 +1082,25 @@
       <c r="E2" s="1">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="str">
+        <f>IF(E2&gt;8,"GIỎI", IF(E2&gt;=6.5,"KHÁ", IF(E2&gt;=5,"TRUNG BÌNH","YẾU")))</f>
+        <v>KHÁ</v>
+      </c>
+      <c r="H2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K2" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="L2" t="str">
+        <f t="shared" ref="L2:L36" si="0">IF(K2&gt;8,"GIỎI", IF(K2&gt;=6.5,"KHÁ", IF(K2&gt;=5,"TRUNG BÌNH","YẾU")))</f>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1055,8 +1116,32 @@
       <c r="E3" s="1">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F37" si="1">IF(E3&gt;8,"GIỎI", IF(E3&gt;=6.5,"KHÁ", IF(E3&gt;=5,"TRUNG BÌNH","YẾU")))</f>
+        <v>KHÁ</v>
+      </c>
+      <c r="H3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K3" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="L3" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="N3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O3">
+        <f>COUNTIF($L$1:$L$36,H1)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1072,8 +1157,32 @@
       <c r="E4" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="str">
+        <f t="shared" si="1"/>
+        <v>GIỎI</v>
+      </c>
+      <c r="H4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K4" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="L4" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="N4" t="s">
+        <v>93</v>
+      </c>
+      <c r="O4">
+        <f>COUNTIF($L$1:$L$36,N4)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -1089,8 +1198,26 @@
       <c r="E5" s="1">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K5" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="N5" t="s">
+        <v>95</v>
+      </c>
+      <c r="O5">
+        <f>COUNTIF($L$1:$L$36,N5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -1106,8 +1233,26 @@
       <c r="E6" s="1">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K6" s="1">
+        <v>8.9</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+      <c r="N6" t="s">
+        <v>97</v>
+      </c>
+      <c r="O6">
+        <f>COUNTIF($L$1:$L$36,N6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -1123,8 +1268,19 @@
       <c r="E7" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K7" s="1">
+        <v>7.85</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -1140,8 +1296,19 @@
       <c r="E8" s="1">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K8" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -1157,8 +1324,26 @@
       <c r="E9" s="1">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="H9">
+        <f>COUNTIF($F$2:$F$37,H2)</f>
+        <v>24</v>
+      </c>
+      <c r="I9" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" s="1">
+        <v>8</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1174,8 +1359,26 @@
       <c r="E10" s="1">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="H10">
+        <f>COUNTIF($F$2:$F$37,H1)</f>
+        <v>12</v>
+      </c>
+      <c r="I10" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="L10" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1191,8 +1394,19 @@
       <c r="E11" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K11" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="L11" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1208,8 +1422,19 @@
       <c r="E12" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K12" s="1">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1225,8 +1450,19 @@
       <c r="E13" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K13" s="1">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="L13" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1242,8 +1478,19 @@
       <c r="E14" s="1">
         <v>9.5</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" t="str">
+        <f t="shared" si="1"/>
+        <v>GIỎI</v>
+      </c>
+      <c r="K14" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="L14" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1259,8 +1506,19 @@
       <c r="E15" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K15" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="L15" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1276,8 +1534,19 @@
       <c r="E16" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" t="str">
+        <f t="shared" si="1"/>
+        <v>GIỎI</v>
+      </c>
+      <c r="K16" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -1293,8 +1562,19 @@
       <c r="E17" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K17" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -1310,8 +1590,19 @@
       <c r="E18" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" t="str">
+        <f t="shared" si="1"/>
+        <v>GIỎI</v>
+      </c>
+      <c r="K18" s="1">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="L18" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -1327,8 +1618,19 @@
       <c r="E19" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" t="str">
+        <f t="shared" si="1"/>
+        <v>GIỎI</v>
+      </c>
+      <c r="K19" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="L19" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1344,8 +1646,19 @@
       <c r="E20" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" t="str">
+        <f t="shared" si="1"/>
+        <v>GIỎI</v>
+      </c>
+      <c r="K20" s="1">
+        <v>9</v>
+      </c>
+      <c r="L20" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1674,19 @@
       <c r="E21" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K21" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="L21" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -1378,8 +1702,19 @@
       <c r="E22" s="1">
         <v>8.9</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" t="str">
+        <f t="shared" si="1"/>
+        <v>GIỎI</v>
+      </c>
+      <c r="K22" s="1">
+        <v>9.35</v>
+      </c>
+      <c r="L22" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -1395,8 +1730,19 @@
       <c r="E23" s="1">
         <v>8.6</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" t="str">
+        <f t="shared" si="1"/>
+        <v>GIỎI</v>
+      </c>
+      <c r="K23" s="1">
+        <v>9.35</v>
+      </c>
+      <c r="L23" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -1412,8 +1758,19 @@
       <c r="E24" s="1">
         <v>7.8</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K24" s="1">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="L24" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -1429,8 +1786,19 @@
       <c r="E25" s="1">
         <v>7.8</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K25" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="L25" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -1446,8 +1814,19 @@
       <c r="E26" s="1">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K26" s="1">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L26" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1463,8 +1842,19 @@
       <c r="E27" s="1">
         <v>9.5</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" t="str">
+        <f t="shared" si="1"/>
+        <v>GIỎI</v>
+      </c>
+      <c r="K27" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="L27" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -1480,8 +1870,19 @@
       <c r="E28" s="1">
         <v>8.6</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" t="str">
+        <f t="shared" si="1"/>
+        <v>GIỎI</v>
+      </c>
+      <c r="K28" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="L28" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -1497,8 +1898,19 @@
       <c r="E29" s="1">
         <v>9.5</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" t="str">
+        <f t="shared" si="1"/>
+        <v>GIỎI</v>
+      </c>
+      <c r="K29" s="1">
+        <v>8.75</v>
+      </c>
+      <c r="L29" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -1514,8 +1926,19 @@
       <c r="E30" s="1">
         <v>8.5</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" t="str">
+        <f t="shared" si="1"/>
+        <v>GIỎI</v>
+      </c>
+      <c r="K30" s="1">
+        <v>8.75</v>
+      </c>
+      <c r="L30" t="str">
+        <f t="shared" si="0"/>
+        <v>GIỎI</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -1531,8 +1954,19 @@
       <c r="E31" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K31" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="L31" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -1548,8 +1982,19 @@
       <c r="E32" s="1">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K32" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="L32" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -1565,8 +2010,19 @@
       <c r="E33" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K33" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="L33" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -1582,8 +2038,19 @@
       <c r="E34" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K34" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="L34" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -1599,8 +2066,19 @@
       <c r="E35" s="1">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K35" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="L35" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -1616,8 +2094,19 @@
       <c r="E36" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
+      </c>
+      <c r="K36" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="L36" t="str">
+        <f t="shared" si="0"/>
+        <v>KHÁ</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -1632,6 +2121,10 @@
       </c>
       <c r="E37" s="1">
         <v>7.5</v>
+      </c>
+      <c r="F37" t="str">
+        <f t="shared" si="1"/>
+        <v>KHÁ</v>
       </c>
     </row>
   </sheetData>

--- a/grading_results_rag_metrics.xlsx
+++ b/grading_results_rag_metrics.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UEH\Downloads\17. Đề án tốt nghiệp\rag\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\rag\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE7F4F7-4705-47A4-9288-987B0F69600F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C8A8C8-7658-4E50-B5AF-70AEA491BC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1575" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="91">
   <si>
     <t>Chiến lược kinh doanh thương mại điện tử</t>
   </si>
@@ -653,36 +653,6 @@
   </si>
   <si>
     <t>diem_mo_hinh_rag</t>
-  </si>
-  <si>
-    <t>GIỎI</t>
-  </si>
-  <si>
-    <t>&gt;8</t>
-  </si>
-  <si>
-    <t>KHÁ</t>
-  </si>
-  <si>
-    <t>6.5-7.9</t>
-  </si>
-  <si>
-    <t>TRUNG BÌNH</t>
-  </si>
-  <si>
-    <t>5-6.4</t>
-  </si>
-  <si>
-    <t>YẾU</t>
-  </si>
-  <si>
-    <t>&lt;5</t>
-  </si>
-  <si>
-    <t>khá</t>
-  </si>
-  <si>
-    <t>giỏi</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +995,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.42578125" bestFit="1" customWidth="1"/>
@@ -1033,10 +1003,9 @@
     <col min="3" max="3" width="51.5703125" customWidth="1"/>
     <col min="4" max="4" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>86</v>
       </c>
@@ -1052,21 +1021,8 @@
       <c r="E1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K1" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="L1" t="str">
-        <f>IF(K1&gt;8,"GIỎI", IF(K1&gt;=6.5,"KHÁ", IF(K1&gt;=5,"TRUNG BÌNH","YẾU")))</f>
-        <v>KHÁ</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1082,25 +1038,8 @@
       <c r="E2" s="1">
         <v>7.5</v>
       </c>
-      <c r="F2" t="str">
-        <f>IF(E2&gt;8,"GIỎI", IF(E2&gt;=6.5,"KHÁ", IF(E2&gt;=5,"TRUNG BÌNH","YẾU")))</f>
-        <v>KHÁ</v>
-      </c>
-      <c r="H2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K2" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="L2" t="str">
-        <f t="shared" ref="L2:L36" si="0">IF(K2&gt;8,"GIỎI", IF(K2&gt;=6.5,"KHÁ", IF(K2&gt;=5,"TRUNG BÌNH","YẾU")))</f>
-        <v>KHÁ</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1116,32 +1055,8 @@
       <c r="E3" s="1">
         <v>7.5</v>
       </c>
-      <c r="F3" t="str">
-        <f t="shared" ref="F3:F37" si="1">IF(E3&gt;8,"GIỎI", IF(E3&gt;=6.5,"KHÁ", IF(E3&gt;=5,"TRUNG BÌNH","YẾU")))</f>
-        <v>KHÁ</v>
-      </c>
-      <c r="H3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I3" t="s">
-        <v>96</v>
-      </c>
-      <c r="K3" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="L3" t="str">
-        <f t="shared" si="0"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="N3" t="s">
-        <v>91</v>
-      </c>
-      <c r="O3">
-        <f>COUNTIF($L$1:$L$36,H1)</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1157,32 +1072,8 @@
       <c r="E4" s="1">
         <v>9</v>
       </c>
-      <c r="F4" t="str">
-        <f t="shared" si="1"/>
-        <v>GIỎI</v>
-      </c>
-      <c r="H4" t="s">
-        <v>97</v>
-      </c>
-      <c r="I4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K4" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="L4" t="str">
-        <f t="shared" si="0"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="N4" t="s">
-        <v>93</v>
-      </c>
-      <c r="O4">
-        <f>COUNTIF($L$1:$L$36,N4)</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -1198,26 +1089,8 @@
       <c r="E5" s="1">
         <v>7.5</v>
       </c>
-      <c r="F5" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K5" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="L5" t="str">
-        <f t="shared" si="0"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="N5" t="s">
-        <v>95</v>
-      </c>
-      <c r="O5">
-        <f>COUNTIF($L$1:$L$36,N5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -1233,26 +1106,8 @@
       <c r="E6" s="1">
         <v>7.5</v>
       </c>
-      <c r="F6" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K6" s="1">
-        <v>8.9</v>
-      </c>
-      <c r="L6" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-      <c r="N6" t="s">
-        <v>97</v>
-      </c>
-      <c r="O6">
-        <f>COUNTIF($L$1:$L$36,N6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -1268,19 +1123,8 @@
       <c r="E7" s="1">
         <v>7</v>
       </c>
-      <c r="F7" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K7" s="1">
-        <v>7.85</v>
-      </c>
-      <c r="L7" t="str">
-        <f t="shared" si="0"/>
-        <v>KHÁ</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -1296,19 +1140,8 @@
       <c r="E8" s="1">
         <v>7.5</v>
       </c>
-      <c r="F8" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K8" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="L8" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -1324,26 +1157,8 @@
       <c r="E9" s="1">
         <v>7.5</v>
       </c>
-      <c r="F9" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="H9">
-        <f>COUNTIF($F$2:$F$37,H2)</f>
-        <v>24</v>
-      </c>
-      <c r="I9" t="s">
-        <v>99</v>
-      </c>
-      <c r="K9" s="1">
-        <v>8</v>
-      </c>
-      <c r="L9" t="str">
-        <f t="shared" si="0"/>
-        <v>KHÁ</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1359,26 +1174,8 @@
       <c r="E10" s="1">
         <v>7.5</v>
       </c>
-      <c r="F10" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="H10">
-        <f>COUNTIF($F$2:$F$37,H1)</f>
-        <v>12</v>
-      </c>
-      <c r="I10" t="s">
-        <v>100</v>
-      </c>
-      <c r="K10" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="L10" t="str">
-        <f t="shared" si="0"/>
-        <v>KHÁ</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1394,19 +1191,8 @@
       <c r="E11" s="1">
         <v>8</v>
       </c>
-      <c r="F11" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K11" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="L11" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1422,19 +1208,8 @@
       <c r="E12" s="1">
         <v>8</v>
       </c>
-      <c r="F12" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K12" s="1">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="L12" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1450,19 +1225,8 @@
       <c r="E13" s="1">
         <v>8</v>
       </c>
-      <c r="F13" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K13" s="1">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="L13" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1478,19 +1242,8 @@
       <c r="E14" s="1">
         <v>9.5</v>
       </c>
-      <c r="F14" t="str">
-        <f t="shared" si="1"/>
-        <v>GIỎI</v>
-      </c>
-      <c r="K14" s="1">
-        <v>7.6</v>
-      </c>
-      <c r="L14" t="str">
-        <f t="shared" si="0"/>
-        <v>KHÁ</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1506,19 +1259,8 @@
       <c r="E15" s="1">
         <v>8</v>
       </c>
-      <c r="F15" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K15" s="1">
-        <v>8.6</v>
-      </c>
-      <c r="L15" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1534,19 +1276,8 @@
       <c r="E16" s="1">
         <v>9</v>
       </c>
-      <c r="F16" t="str">
-        <f t="shared" si="1"/>
-        <v>GIỎI</v>
-      </c>
-      <c r="K16" s="1">
-        <v>8.4</v>
-      </c>
-      <c r="L16" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -1562,19 +1293,8 @@
       <c r="E17" s="1">
         <v>8</v>
       </c>
-      <c r="F17" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K17" s="1">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="L17" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -1590,19 +1310,8 @@
       <c r="E18" s="1">
         <v>9</v>
       </c>
-      <c r="F18" t="str">
-        <f t="shared" si="1"/>
-        <v>GIỎI</v>
-      </c>
-      <c r="K18" s="1">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="L18" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -1618,19 +1327,8 @@
       <c r="E19" s="1">
         <v>9</v>
       </c>
-      <c r="F19" t="str">
-        <f t="shared" si="1"/>
-        <v>GIỎI</v>
-      </c>
-      <c r="K19" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="L19" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1646,19 +1344,8 @@
       <c r="E20" s="1">
         <v>9</v>
       </c>
-      <c r="F20" t="str">
-        <f t="shared" si="1"/>
-        <v>GIỎI</v>
-      </c>
-      <c r="K20" s="1">
-        <v>9</v>
-      </c>
-      <c r="L20" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1674,19 +1361,8 @@
       <c r="E21" s="1">
         <v>8</v>
       </c>
-      <c r="F21" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K21" s="1">
-        <v>7.6</v>
-      </c>
-      <c r="L21" t="str">
-        <f t="shared" si="0"/>
-        <v>KHÁ</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -1702,19 +1378,8 @@
       <c r="E22" s="1">
         <v>8.9</v>
       </c>
-      <c r="F22" t="str">
-        <f t="shared" si="1"/>
-        <v>GIỎI</v>
-      </c>
-      <c r="K22" s="1">
-        <v>9.35</v>
-      </c>
-      <c r="L22" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -1730,19 +1395,8 @@
       <c r="E23" s="1">
         <v>8.6</v>
       </c>
-      <c r="F23" t="str">
-        <f t="shared" si="1"/>
-        <v>GIỎI</v>
-      </c>
-      <c r="K23" s="1">
-        <v>9.35</v>
-      </c>
-      <c r="L23" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -1758,19 +1412,8 @@
       <c r="E24" s="1">
         <v>7.8</v>
       </c>
-      <c r="F24" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K24" s="1">
-        <v>9.5500000000000007</v>
-      </c>
-      <c r="L24" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -1786,19 +1429,8 @@
       <c r="E25" s="1">
         <v>7.8</v>
       </c>
-      <c r="F25" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K25" s="1">
-        <v>6.8</v>
-      </c>
-      <c r="L25" t="str">
-        <f t="shared" si="0"/>
-        <v>KHÁ</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -1814,19 +1446,8 @@
       <c r="E26" s="1">
         <v>7.5</v>
       </c>
-      <c r="F26" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K26" s="1">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="L26" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1842,19 +1463,8 @@
       <c r="E27" s="1">
         <v>9.5</v>
       </c>
-      <c r="F27" t="str">
-        <f t="shared" si="1"/>
-        <v>GIỎI</v>
-      </c>
-      <c r="K27" s="1">
-        <v>9.5</v>
-      </c>
-      <c r="L27" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -1870,19 +1480,8 @@
       <c r="E28" s="1">
         <v>8.6</v>
       </c>
-      <c r="F28" t="str">
-        <f t="shared" si="1"/>
-        <v>GIỎI</v>
-      </c>
-      <c r="K28" s="1">
-        <v>9.5</v>
-      </c>
-      <c r="L28" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -1898,19 +1497,8 @@
       <c r="E29" s="1">
         <v>9.5</v>
       </c>
-      <c r="F29" t="str">
-        <f t="shared" si="1"/>
-        <v>GIỎI</v>
-      </c>
-      <c r="K29" s="1">
-        <v>8.75</v>
-      </c>
-      <c r="L29" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -1926,19 +1514,8 @@
       <c r="E30" s="1">
         <v>8.5</v>
       </c>
-      <c r="F30" t="str">
-        <f t="shared" si="1"/>
-        <v>GIỎI</v>
-      </c>
-      <c r="K30" s="1">
-        <v>8.75</v>
-      </c>
-      <c r="L30" t="str">
-        <f t="shared" si="0"/>
-        <v>GIỎI</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -1954,19 +1531,8 @@
       <c r="E31" s="1">
         <v>8</v>
       </c>
-      <c r="F31" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K31" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="L31" t="str">
-        <f t="shared" si="0"/>
-        <v>KHÁ</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -1982,19 +1548,8 @@
       <c r="E32" s="1">
         <v>7.5</v>
       </c>
-      <c r="F32" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K32" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="L32" t="str">
-        <f t="shared" si="0"/>
-        <v>KHÁ</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -2010,19 +1565,8 @@
       <c r="E33" s="1">
         <v>8</v>
       </c>
-      <c r="F33" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K33" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="L33" t="str">
-        <f t="shared" si="0"/>
-        <v>KHÁ</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -2038,19 +1582,8 @@
       <c r="E34" s="1">
         <v>7</v>
       </c>
-      <c r="F34" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K34" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="L34" t="str">
-        <f t="shared" si="0"/>
-        <v>KHÁ</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -2066,19 +1599,8 @@
       <c r="E35" s="1">
         <v>7.5</v>
       </c>
-      <c r="F35" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K35" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="L35" t="str">
-        <f t="shared" si="0"/>
-        <v>KHÁ</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -2094,19 +1616,8 @@
       <c r="E36" s="1">
         <v>8</v>
       </c>
-      <c r="F36" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
-      </c>
-      <c r="K36" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="L36" t="str">
-        <f t="shared" si="0"/>
-        <v>KHÁ</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -2121,10 +1632,6 @@
       </c>
       <c r="E37" s="1">
         <v>7.5</v>
-      </c>
-      <c r="F37" t="str">
-        <f t="shared" si="1"/>
-        <v>KHÁ</v>
       </c>
     </row>
   </sheetData>
